--- a/docs/spiderling_example.xlsx
+++ b/docs/spiderling_example.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试控制赋值" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试控件赋值" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试循环" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试跳转" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -421,32 +421,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID (id)</t>
+          <t>序号 (id)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Step Name (name)</t>
+          <t>步骤名称 (name)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Action Type (action)</t>
+          <t>动作类型 (action)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description (description)</t>
+          <t>描述 (description)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CSS Selector (selector)</t>
+          <t>CSS选择器 (selector)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Extract Attribute (attribute)</t>
+          <t>提取属性 (attribute)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Save Variable (variable)</t>
+          <t>保存变量 (variable)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -466,42 +466,42 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Input Text (input)</t>
+          <t>输入文本 (input)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Wait Time (wait)</t>
+          <t>等待时间 (wait)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Timeout (timeout)</t>
+          <t>超时时间 (timeout)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Cache Variable (cache)</t>
+          <t>提取变量 (cache)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Cache Type (source_type)</t>
+          <t>缓存类型 (source_type)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>DataFrame Data Transformation (stage_type)</t>
+          <t>DataFrame数据转换 (stage_type)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Field Remap (remap)</t>
+          <t>字段转义 (remap)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Ignore Error (ignore_error)</t>
+          <t>忽略错误 (ignore_error)</t>
         </is>
       </c>
     </row>
@@ -1293,32 +1293,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID (id)</t>
+          <t>序号 (id)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Step Name (name)</t>
+          <t>步骤名称 (name)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Action Type (action)</t>
+          <t>动作类型 (action)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description (description)</t>
+          <t>描述 (description)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CSS Selector (selector)</t>
+          <t>CSS选择器 (selector)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Extract Attribute (attribute)</t>
+          <t>提取属性 (attribute)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Save Variable (variable)</t>
+          <t>保存变量 (variable)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1338,42 +1338,42 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Input Text (input)</t>
+          <t>输入文本 (input)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Wait Time (wait)</t>
+          <t>等待时间 (wait)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Timeout (timeout)</t>
+          <t>超时时间 (timeout)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Cache Variable (cache)</t>
+          <t>提取变量 (cache)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Cache Type (source_type)</t>
+          <t>缓存类型 (source_type)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>DataFrame Data Transformation (stage_type)</t>
+          <t>DataFrame数据转换 (stage_type)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Field Remap (remap)</t>
+          <t>字段转义 (remap)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Ignore Error (ignore_error)</t>
+          <t>忽略错误 (ignore_error)</t>
         </is>
       </c>
     </row>
@@ -2161,32 +2161,32 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID (id)</t>
+          <t>序号 (id)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Step Name (name)</t>
+          <t>步骤名称 (name)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Action Type (action)</t>
+          <t>动作类型 (action)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Description (description)</t>
+          <t>描述 (description)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CSS Selector (selector)</t>
+          <t>CSS选择器 (selector)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Extract Attribute (attribute)</t>
+          <t>提取属性 (attribute)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Save Variable (variable)</t>
+          <t>保存变量 (variable)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -2206,42 +2206,42 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Input Text (input)</t>
+          <t>输入文本 (input)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Wait Time (wait)</t>
+          <t>等待时间 (wait)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Timeout (timeout)</t>
+          <t>超时时间 (timeout)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Cache Variable (cache)</t>
+          <t>提取变量 (cache)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Cache Type (source_type)</t>
+          <t>缓存类型 (source_type)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>DataFrame Data Transformation (stage_type)</t>
+          <t>DataFrame数据转换 (stage_type)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Field Remap (remap)</t>
+          <t>字段转义 (remap)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Ignore Error (ignore_error)</t>
+          <t>忽略错误 (ignore_error)</t>
         </is>
       </c>
     </row>
